--- a/artfynd/A 29429-2025 artfynd.xlsx
+++ b/artfynd/A 29429-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126837950</v>
       </c>
       <c r="B2" t="n">
-        <v>98395</v>
+        <v>98470</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126837972</v>
       </c>
       <c r="B3" t="n">
-        <v>100543</v>
+        <v>100618</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126837931</v>
       </c>
       <c r="B4" t="n">
-        <v>91210</v>
+        <v>91284</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126837969</v>
       </c>
       <c r="B5" t="n">
-        <v>100543</v>
+        <v>100618</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126837967</v>
       </c>
       <c r="B6" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 29429-2025 artfynd.xlsx
+++ b/artfynd/A 29429-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126837950</v>
       </c>
       <c r="B2" t="n">
-        <v>98470</v>
+        <v>98476</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126837972</v>
       </c>
       <c r="B3" t="n">
-        <v>100618</v>
+        <v>100624</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126837931</v>
       </c>
       <c r="B4" t="n">
-        <v>91284</v>
+        <v>91290</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126837969</v>
       </c>
       <c r="B5" t="n">
-        <v>100618</v>
+        <v>100624</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126837967</v>
       </c>
       <c r="B6" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 29429-2025 artfynd.xlsx
+++ b/artfynd/A 29429-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126837950</v>
       </c>
       <c r="B2" t="n">
-        <v>98476</v>
+        <v>98477</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126837972</v>
       </c>
       <c r="B3" t="n">
-        <v>100624</v>
+        <v>100625</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126837931</v>
       </c>
       <c r="B4" t="n">
-        <v>91290</v>
+        <v>91291</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126837969</v>
       </c>
       <c r="B5" t="n">
-        <v>100624</v>
+        <v>100625</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126837967</v>
       </c>
       <c r="B6" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 29429-2025 artfynd.xlsx
+++ b/artfynd/A 29429-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126837950</v>
       </c>
       <c r="B2" t="n">
-        <v>98477</v>
+        <v>98481</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126837972</v>
       </c>
       <c r="B3" t="n">
-        <v>100625</v>
+        <v>100629</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126837931</v>
       </c>
       <c r="B4" t="n">
-        <v>91291</v>
+        <v>91295</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126837969</v>
       </c>
       <c r="B5" t="n">
-        <v>100625</v>
+        <v>100629</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126837967</v>
       </c>
       <c r="B6" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 29429-2025 artfynd.xlsx
+++ b/artfynd/A 29429-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126837950</v>
       </c>
       <c r="B2" t="n">
-        <v>98481</v>
+        <v>98482</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126837972</v>
       </c>
       <c r="B3" t="n">
-        <v>100629</v>
+        <v>100630</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126837969</v>
       </c>
       <c r="B5" t="n">
-        <v>100629</v>
+        <v>100630</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126837967</v>
       </c>
       <c r="B6" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 29429-2025 artfynd.xlsx
+++ b/artfynd/A 29429-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126837950</v>
       </c>
       <c r="B2" t="n">
-        <v>98482</v>
+        <v>98470</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126837972</v>
       </c>
       <c r="B3" t="n">
-        <v>100630</v>
+        <v>100618</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126837931</v>
       </c>
       <c r="B4" t="n">
-        <v>91295</v>
+        <v>91284</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126837969</v>
       </c>
       <c r="B5" t="n">
-        <v>100630</v>
+        <v>100618</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126837967</v>
       </c>
       <c r="B6" t="n">
-        <v>98448</v>
+        <v>98436</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 29429-2025 artfynd.xlsx
+++ b/artfynd/A 29429-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126837950</v>
       </c>
       <c r="B2" t="n">
-        <v>98470</v>
+        <v>98482</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126837972</v>
       </c>
       <c r="B3" t="n">
-        <v>100618</v>
+        <v>100630</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126837931</v>
       </c>
       <c r="B4" t="n">
-        <v>91284</v>
+        <v>91295</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126837969</v>
       </c>
       <c r="B5" t="n">
-        <v>100618</v>
+        <v>100630</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126837967</v>
       </c>
       <c r="B6" t="n">
-        <v>98436</v>
+        <v>98448</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 29429-2025 artfynd.xlsx
+++ b/artfynd/A 29429-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1158,6 +1158,920 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>132009025</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101251</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lintjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>514069</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6757477</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>132009587</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99046</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lintjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>514154</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6757482</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>132011346</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79268</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lintjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>514102</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6757458</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>132011185</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91860</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lintjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>514121</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6757471</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>132012809</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99046</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lintjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>514113</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6757269</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>132010406</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99046</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lintjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>514098</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6757561</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>132009538</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91840</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lintjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>514154</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6757482</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>132009422</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92139</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>658</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lintjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>514154</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6757482</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29429-2025 artfynd.xlsx
+++ b/artfynd/A 29429-2025 artfynd.xlsx
@@ -1610,7 +1610,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132012809</v>
+        <v>132010406</v>
       </c>
       <c r="B11" t="n">
         <v>99046</v>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1654,10 +1654,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514113</v>
+        <v>514098</v>
       </c>
       <c r="R11" t="n">
-        <v>6757269</v>
+        <v>6757561</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1726,7 +1726,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132010406</v>
+        <v>132012809</v>
       </c>
       <c r="B12" t="n">
         <v>99046</v>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514098</v>
+        <v>514113</v>
       </c>
       <c r="R12" t="n">
-        <v>6757561</v>
+        <v>6757269</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 29429-2025 artfynd.xlsx
+++ b/artfynd/A 29429-2025 artfynd.xlsx
@@ -1163,7 +1163,7 @@
         <v>132009025</v>
       </c>
       <c r="B7" t="n">
-        <v>101251</v>
+        <v>101252</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>132009587</v>
       </c>
       <c r="B8" t="n">
-        <v>99046</v>
+        <v>99047</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>132011346</v>
       </c>
       <c r="B9" t="n">
-        <v>79268</v>
+        <v>79269</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>132011185</v>
       </c>
       <c r="B10" t="n">
-        <v>91860</v>
+        <v>91861</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,10 +1610,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132010406</v>
+        <v>132012809</v>
       </c>
       <c r="B11" t="n">
-        <v>99046</v>
+        <v>99047</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1654,10 +1654,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514098</v>
+        <v>514113</v>
       </c>
       <c r="R11" t="n">
-        <v>6757561</v>
+        <v>6757269</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1726,10 +1726,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132012809</v>
+        <v>132010406</v>
       </c>
       <c r="B12" t="n">
-        <v>99046</v>
+        <v>99047</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514113</v>
+        <v>514098</v>
       </c>
       <c r="R12" t="n">
-        <v>6757269</v>
+        <v>6757561</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1845,7 +1845,7 @@
         <v>132009538</v>
       </c>
       <c r="B13" t="n">
-        <v>91840</v>
+        <v>91841</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>132009422</v>
       </c>
       <c r="B14" t="n">
-        <v>92139</v>
+        <v>92140</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 29429-2025 artfynd.xlsx
+++ b/artfynd/A 29429-2025 artfynd.xlsx
@@ -1163,7 +1163,7 @@
         <v>132009025</v>
       </c>
       <c r="B7" t="n">
-        <v>101252</v>
+        <v>101257</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>132009587</v>
       </c>
       <c r="B8" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>132011346</v>
       </c>
       <c r="B9" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>132011185</v>
       </c>
       <c r="B10" t="n">
-        <v>91861</v>
+        <v>91866</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>132012809</v>
       </c>
       <c r="B11" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>132010406</v>
       </c>
       <c r="B12" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         <v>132009538</v>
       </c>
       <c r="B13" t="n">
-        <v>91841</v>
+        <v>91846</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>132009422</v>
       </c>
       <c r="B14" t="n">
-        <v>92140</v>
+        <v>92145</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 29429-2025 artfynd.xlsx
+++ b/artfynd/A 29429-2025 artfynd.xlsx
@@ -1163,7 +1163,7 @@
         <v>132009025</v>
       </c>
       <c r="B7" t="n">
-        <v>101257</v>
+        <v>101260</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>132009587</v>
       </c>
       <c r="B8" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>132011346</v>
       </c>
       <c r="B9" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>132011185</v>
       </c>
       <c r="B10" t="n">
-        <v>91866</v>
+        <v>91868</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>132012809</v>
       </c>
       <c r="B11" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>132010406</v>
       </c>
       <c r="B12" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         <v>132009538</v>
       </c>
       <c r="B13" t="n">
-        <v>91846</v>
+        <v>91848</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>132009422</v>
       </c>
       <c r="B14" t="n">
-        <v>92145</v>
+        <v>92147</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 29429-2025 artfynd.xlsx
+++ b/artfynd/A 29429-2025 artfynd.xlsx
@@ -1163,7 +1163,7 @@
         <v>132009025</v>
       </c>
       <c r="B7" t="n">
-        <v>101260</v>
+        <v>101296</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>132009587</v>
       </c>
       <c r="B8" t="n">
-        <v>99054</v>
+        <v>99090</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>132011346</v>
       </c>
       <c r="B9" t="n">
-        <v>79276</v>
+        <v>79310</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>132011185</v>
       </c>
       <c r="B10" t="n">
-        <v>91868</v>
+        <v>91904</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>132012809</v>
       </c>
       <c r="B11" t="n">
-        <v>99054</v>
+        <v>99090</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>132010406</v>
       </c>
       <c r="B12" t="n">
-        <v>99054</v>
+        <v>99090</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         <v>132009538</v>
       </c>
       <c r="B13" t="n">
-        <v>91848</v>
+        <v>91884</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>132009422</v>
       </c>
       <c r="B14" t="n">
-        <v>92147</v>
+        <v>92183</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 29429-2025 artfynd.xlsx
+++ b/artfynd/A 29429-2025 artfynd.xlsx
@@ -1163,7 +1163,7 @@
         <v>132009025</v>
       </c>
       <c r="B7" t="n">
-        <v>101301</v>
+        <v>101304</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>132009587</v>
       </c>
       <c r="B8" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>132011346</v>
       </c>
       <c r="B9" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>132011185</v>
       </c>
       <c r="B10" t="n">
-        <v>91909</v>
+        <v>91912</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>132012809</v>
       </c>
       <c r="B11" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>132010406</v>
       </c>
       <c r="B12" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         <v>132009538</v>
       </c>
       <c r="B13" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>132009422</v>
       </c>
       <c r="B14" t="n">
-        <v>92188</v>
+        <v>92191</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 29429-2025 artfynd.xlsx
+++ b/artfynd/A 29429-2025 artfynd.xlsx
@@ -1163,7 +1163,7 @@
         <v>132009025</v>
       </c>
       <c r="B7" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>132009587</v>
       </c>
       <c r="B8" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>132011346</v>
       </c>
       <c r="B9" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>132011185</v>
       </c>
       <c r="B10" t="n">
-        <v>91912</v>
+        <v>91918</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>132012809</v>
       </c>
       <c r="B11" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>132010406</v>
       </c>
       <c r="B12" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         <v>132009538</v>
       </c>
       <c r="B13" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>132009422</v>
       </c>
       <c r="B14" t="n">
-        <v>92191</v>
+        <v>92197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 29429-2025 artfynd.xlsx
+++ b/artfynd/A 29429-2025 artfynd.xlsx
@@ -1163,7 +1163,7 @@
         <v>132009025</v>
       </c>
       <c r="B7" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>132009587</v>
       </c>
       <c r="B8" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>132011346</v>
       </c>
       <c r="B9" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>132011185</v>
       </c>
       <c r="B10" t="n">
-        <v>91918</v>
+        <v>91928</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>132012809</v>
       </c>
       <c r="B11" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>132010406</v>
       </c>
       <c r="B12" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         <v>132009538</v>
       </c>
       <c r="B13" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>132009422</v>
       </c>
       <c r="B14" t="n">
-        <v>92197</v>
+        <v>92207</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 29429-2025 artfynd.xlsx
+++ b/artfynd/A 29429-2025 artfynd.xlsx
@@ -1163,7 +1163,7 @@
         <v>132009025</v>
       </c>
       <c r="B7" t="n">
-        <v>101323</v>
+        <v>101325</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>132009587</v>
       </c>
       <c r="B8" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>132011185</v>
       </c>
       <c r="B10" t="n">
-        <v>91928</v>
+        <v>91929</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>132012809</v>
       </c>
       <c r="B11" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>132010406</v>
       </c>
       <c r="B12" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         <v>132009538</v>
       </c>
       <c r="B13" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>132009422</v>
       </c>
       <c r="B14" t="n">
-        <v>92207</v>
+        <v>92208</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 29429-2025 artfynd.xlsx
+++ b/artfynd/A 29429-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,45 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126837950</v>
+        <v>132009422</v>
       </c>
       <c r="B2" t="n">
-        <v>98482</v>
+        <v>92245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219874</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Born, Dlr</t>
+          <t>Lintjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514178</v>
+        <v>514154</v>
       </c>
       <c r="R2" t="n">
-        <v>6757313</v>
+        <v>6757482</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,12 +749,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,57 +779,66 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126837972</v>
+        <v>132009538</v>
       </c>
       <c r="B3" t="n">
-        <v>100630</v>
+        <v>91974</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Born, Dlr</t>
+          <t>Lintjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514153</v>
+        <v>514154</v>
       </c>
       <c r="R3" t="n">
-        <v>6757646</v>
+        <v>6757482</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -837,12 +865,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -857,12 +895,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -872,7 +910,7 @@
         <v>126837931</v>
       </c>
       <c r="B4" t="n">
-        <v>91295</v>
+        <v>91872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,45 +1004,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126837969</v>
+        <v>132011346</v>
       </c>
       <c r="B5" t="n">
-        <v>100630</v>
+        <v>79373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Born, Dlr</t>
+          <t>Lintjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514019</v>
+        <v>514102</v>
       </c>
       <c r="R5" t="n">
-        <v>6757359</v>
+        <v>6757458</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1031,12 +1078,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1051,57 +1108,62 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126837967</v>
+        <v>132008652</v>
       </c>
       <c r="B6" t="n">
-        <v>98448</v>
+        <v>57972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Born, Dlr</t>
+          <t>Lintjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514171</v>
+        <v>514007</v>
       </c>
       <c r="R6" t="n">
-        <v>6757320</v>
+        <v>6757453</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1128,12 +1190,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1148,22 +1220,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132009025</v>
+        <v>126837973</v>
       </c>
       <c r="B7" t="n">
-        <v>101326</v>
+        <v>8444</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,38 +1243,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lintjärnen, Dlr</t>
+          <t>Born, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514069</v>
+        <v>514178</v>
       </c>
       <c r="R7" t="n">
-        <v>6757477</v>
+        <v>6757557</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1229,22 +1297,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:11</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:11</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1259,66 +1317,57 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132009587</v>
+        <v>126837950</v>
       </c>
       <c r="B8" t="n">
-        <v>99118</v>
+        <v>99153</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lintjärnen, Dlr</t>
+          <t>Born, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514154</v>
+        <v>514178</v>
       </c>
       <c r="R8" t="n">
-        <v>6757482</v>
+        <v>6757313</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1345,22 +1394,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>14:27</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:27</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1375,66 +1414,57 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132011346</v>
+        <v>126837967</v>
       </c>
       <c r="B9" t="n">
-        <v>79327</v>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lintjärnen, Dlr</t>
+          <t>Born, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514102</v>
+        <v>514171</v>
       </c>
       <c r="R9" t="n">
-        <v>6757458</v>
+        <v>6757320</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1461,22 +1491,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>15:15</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>15:15</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1491,45 +1511,54 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132011185</v>
+        <v>132008521</v>
       </c>
       <c r="B10" t="n">
-        <v>91929</v>
+        <v>99195</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1538,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>514121</v>
+        <v>514007</v>
       </c>
       <c r="R10" t="n">
-        <v>6757471</v>
+        <v>6757453</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1573,7 +1602,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1583,7 +1612,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1610,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132012809</v>
+        <v>132009294</v>
       </c>
       <c r="B11" t="n">
-        <v>99118</v>
+        <v>99195</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1654,10 +1683,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514113</v>
+        <v>514154</v>
       </c>
       <c r="R11" t="n">
-        <v>6757269</v>
+        <v>6757482</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1689,7 +1718,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1699,7 +1728,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1726,10 +1755,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132010406</v>
+        <v>132009740</v>
       </c>
       <c r="B12" t="n">
-        <v>99118</v>
+        <v>99195</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,12 +1785,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1770,10 +1794,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514098</v>
+        <v>514174</v>
       </c>
       <c r="R12" t="n">
-        <v>6757561</v>
+        <v>6757543</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1805,7 +1829,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1815,7 +1839,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1842,42 +1866,42 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132009538</v>
+        <v>132010406</v>
       </c>
       <c r="B13" t="n">
-        <v>91909</v>
+        <v>99195</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1886,10 +1910,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514154</v>
+        <v>514098</v>
       </c>
       <c r="R13" t="n">
-        <v>6757482</v>
+        <v>6757561</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1921,7 +1945,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1931,7 +1955,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1958,42 +1982,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132009422</v>
+        <v>132012536</v>
       </c>
       <c r="B14" t="n">
-        <v>92208</v>
+        <v>99195</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2002,10 +2026,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514154</v>
+        <v>514113</v>
       </c>
       <c r="R14" t="n">
-        <v>6757482</v>
+        <v>6757269</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2037,7 +2061,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2047,7 +2071,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2071,6 +2095,738 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>132013322</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lintjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>513994</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6757319</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>126837934</v>
+      </c>
+      <c r="B16" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Born, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>514224</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6757306</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>126837969</v>
+      </c>
+      <c r="B17" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Born, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>514019</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6757359</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>126837972</v>
+      </c>
+      <c r="B18" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Born, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>514153</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6757646</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>132008409</v>
+      </c>
+      <c r="B19" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Lintjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>514007</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6757453</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>132009025</v>
+      </c>
+      <c r="B20" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Lintjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>514069</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6757477</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>132013399</v>
+      </c>
+      <c r="B21" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Lintjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>513994</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6757319</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
